--- a/output/pdf_financials_xlsx/TG.xlsx
+++ b/output/pdf_financials_xlsx/TG.xlsx
@@ -3672,13 +3672,13 @@
         <v>0.240086</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.221647</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.312078</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.5570580000000001</v>
       </c>
     </row>
     <row r="93">
@@ -4514,28 +4514,28 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.026429</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.114085</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.102466</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.545844</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.515523</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.259819</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-1.241936</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-2.872047</v>
       </c>
     </row>
     <row r="119">
@@ -6005,7 +6005,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12691,7 +12695,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -13367,7 +13375,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TG.xlsx
+++ b/output/pdf_financials_xlsx/TG.xlsx
@@ -792,28 +792,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004065</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003347</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002468</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003183</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.014527</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.029385</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.026981</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.071961</v>
       </c>
     </row>
     <row r="13">
@@ -1374,28 +1374,28 @@
         <v>-0.042973</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.371062</v>
+        <v>-1.375127</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.407094</v>
+        <v>-0.410441</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.542261</v>
+        <v>-0.544729</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.432964</v>
+        <v>-0.436147</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.682612</v>
+        <v>-0.697139</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.203152</v>
+        <v>-0.232537</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.054922</v>
+        <v>-1.081903</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.174018</v>
+        <v>-0.245979</v>
       </c>
     </row>
     <row r="28">
@@ -1442,28 +1442,28 @@
         <v>-0.042973</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.371062</v>
+        <v>-1.375127</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.407094</v>
+        <v>-0.410441</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.542261</v>
+        <v>-0.544729</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.432964</v>
+        <v>-0.436147</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.682612</v>
+        <v>-0.697139</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.203152</v>
+        <v>-0.232537</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.054922</v>
+        <v>-1.081903</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.174018</v>
+        <v>-0.245979</v>
       </c>
     </row>
     <row r="30">
@@ -1618,16 +1618,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.480008</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.341493</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.092561</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.746016</v>
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.517508</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.378993</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.092561</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.746016</v>
@@ -2094,16 +2094,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.107765</v>
+        <v>0.007765</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.505089</v>
+        <v>0.025081</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.358883</v>
+        <v>0.01739</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.100667</v>
+        <v>0.008106</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.072287</v>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">

--- a/output/pdf_financials_xlsx/TG.xlsx
+++ b/output/pdf_financials_xlsx/TG.xlsx
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.03047</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -12035,7 +12035,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -13794,7 +13798,11 @@
           <t>Proceeds from sale of marketable securities 4</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
